--- a/etc/r18-Core_Argo_ConfigurationParameterNames.xlsx
+++ b/etc/r18-Core_Argo_ConfigurationParameterNames.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\DATA\ArgoVocabs\R18\Work\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rcancoue\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71FF15BB-A8C3-4722-90B5-96F4C8335C33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEDCA704-16EA-43F9-8EAF-00C83862BC56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="45" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1947" uniqueCount="1286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1949" uniqueCount="1287">
   <si>
     <t>Configuration Variable Name</t>
   </si>
@@ -3921,9 +3921,6 @@
 Final review</t>
   </si>
   <si>
-    <t>Argo configuration parameters, version x.x, updated on 10 March 2026</t>
-  </si>
-  <si>
     <t>Maximum delay allowed for the float to connect to the RUDICS server. Default value is 30 minutes.</t>
   </si>
   <si>
@@ -4002,6 +3999,12 @@
   </si>
   <si>
     <t>GDAC AUDIT 20260109</t>
+  </si>
+  <si>
+    <t>Argo configuration parameters, version x.x, updated on 9 June 2026</t>
+  </si>
+  <si>
+    <t>CC00062 - CONFIG_GroundingModeDeepZoneThickness_dbar undeprecated</t>
   </si>
 </sst>
 </file>
@@ -4489,21 +4492,6 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="3" fillId="19" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -4522,8 +4510,23 @@
     <xf numFmtId="0" fontId="3" fillId="20" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="21" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -5006,11 +5009,11 @@
       <c r="A1" s="6"/>
     </row>
     <row r="2" spans="1:26" ht="88.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="61" t="s">
         <v>312</v>
       </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
@@ -5158,31 +5161,41 @@
       </c>
     </row>
     <row r="11" spans="1:26" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="60">
+      <c r="A11" s="55">
         <v>46091</v>
       </c>
-      <c r="B11" s="61" t="s">
+      <c r="B11" s="56" t="s">
         <v>1257</v>
       </c>
-      <c r="C11" s="62" t="s">
+      <c r="C11" s="57" t="s">
         <v>1258</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="63">
+      <c r="A12" s="58">
         <v>46092</v>
       </c>
-      <c r="B12" s="64" t="s">
+      <c r="B12" s="59" t="s">
         <v>1257</v>
       </c>
-      <c r="C12" s="65" t="s">
-        <v>1284</v>
+      <c r="C12" s="60" t="s">
+        <v>1283</v>
       </c>
     </row>
-    <row r="13" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="55">
+        <v>46182</v>
+      </c>
+      <c r="B13" s="56" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C13" s="57" t="s">
+        <v>1286</v>
+      </c>
+    </row>
     <row r="14" spans="1:26" ht="26.4" x14ac:dyDescent="0.3">
       <c r="B14" s="6" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="C14" s="49" t="s">
         <v>752</v>
@@ -6154,25 +6167,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.3">
-      <c r="A1" s="57" t="s">
-        <v>1259</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="66" t="s">
+      <c r="A1" s="63" t="s">
         <v>1285</v>
       </c>
-      <c r="I1" s="66"/>
-      <c r="J1" s="56" t="s">
-        <v>1275</v>
-      </c>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="64" t="s">
+        <v>1284</v>
+      </c>
+      <c r="I1" s="64"/>
+      <c r="J1" s="62" t="s">
+        <v>1274</v>
+      </c>
+      <c r="K1" s="62"/>
+      <c r="L1" s="62"/>
+      <c r="M1" s="62"/>
     </row>
     <row r="2" spans="1:13" s="19" customFormat="1" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
@@ -7029,7 +7042,7 @@
         <v>44</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="D28" s="1"/>
       <c r="F28" s="8">
@@ -8138,10 +8151,10 @@
         <v>89</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>5</v>
@@ -8177,9 +8190,7 @@
       </c>
       <c r="D64" s="1"/>
       <c r="F64" s="8"/>
-      <c r="G64" s="8">
-        <v>46090</v>
-      </c>
+      <c r="G64" s="8"/>
       <c r="H64" s="47">
         <f>VLOOKUP(Tableau1[[#This Row],[Configuration Variable Name]],Audit_CPN_LCPN!$B$2:$Z$500,2,FALSE)</f>
         <v>0</v>
@@ -8203,7 +8214,7 @@
         <v>91</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>92</v>
@@ -8300,7 +8311,7 @@
         <v>97</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D68" s="1"/>
       <c r="E68" s="2" t="s">
@@ -8623,7 +8634,7 @@
         <v>1254</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>5</v>
@@ -8841,7 +8852,7 @@
         <v>118</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>119</v>
@@ -8971,7 +8982,7 @@
         <v>379</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>5</v>
@@ -9454,7 +9465,7 @@
         <v>389</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>5</v>
@@ -9515,7 +9526,7 @@
         <v>151</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="D106" s="1"/>
       <c r="E106" s="2" t="s">
@@ -10023,7 +10034,7 @@
         <v>171</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="D122" s="1"/>
       <c r="E122" s="2" t="s">
@@ -10281,7 +10292,7 @@
         <v>182</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>739</v>
@@ -10384,7 +10395,7 @@
         <v>185</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>6</v>
@@ -10483,7 +10494,7 @@
         <v>188</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="D136" s="52" t="s">
         <v>1249</v>
@@ -11123,7 +11134,7 @@
         <v>214</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="D156" s="1"/>
       <c r="E156" s="2" t="s">
@@ -11154,7 +11165,7 @@
         <v>215</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="D157" s="1"/>
       <c r="E157" s="2" t="s">
@@ -11700,10 +11711,10 @@
         <v>236</v>
       </c>
       <c r="C174" s="1" t="s">
+        <v>1280</v>
+      </c>
+      <c r="D174" s="1" t="s">
         <v>1281</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>1282</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>5</v>
@@ -11856,7 +11867,7 @@
         <v>242</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="D179" s="51" t="s">
         <v>1245</v>
@@ -12210,7 +12221,7 @@
         <v>255</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="D190" s="1"/>
       <c r="E190" s="2" t="s">
@@ -13016,7 +13027,7 @@
         <v>285</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="D216" s="1"/>
       <c r="E216" s="2" t="s">
@@ -13307,7 +13318,7 @@
         <v>724</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="E225" s="2" t="s">
         <v>13</v>
@@ -13557,60 +13568,60 @@
       <c r="D1" s="36"/>
       <c r="E1" s="37"/>
       <c r="F1" s="41"/>
-      <c r="G1" s="58" t="s">
+      <c r="G1" s="65" t="s">
         <v>753</v>
       </c>
-      <c r="H1" s="58"/>
-      <c r="I1" s="58"/>
-      <c r="J1" s="58"/>
-      <c r="K1" s="58"/>
-      <c r="L1" s="58"/>
-      <c r="M1" s="58"/>
-      <c r="N1" s="58"/>
-      <c r="O1" s="58"/>
-      <c r="P1" s="58"/>
-      <c r="Q1" s="58"/>
-      <c r="R1" s="58"/>
-      <c r="S1" s="58"/>
-      <c r="T1" s="58"/>
-      <c r="U1" s="58"/>
-      <c r="V1" s="58"/>
-      <c r="W1" s="58"/>
-      <c r="X1" s="58"/>
-      <c r="Y1" s="58"/>
-      <c r="Z1" s="58"/>
-      <c r="AA1" s="58"/>
-      <c r="AB1" s="58"/>
-      <c r="AC1" s="58"/>
-      <c r="AD1" s="58"/>
-      <c r="AE1" s="58"/>
-      <c r="AF1" s="58"/>
-      <c r="AG1" s="58"/>
-      <c r="AH1" s="58"/>
-      <c r="AI1" s="58"/>
-      <c r="AJ1" s="58"/>
-      <c r="AK1" s="58"/>
-      <c r="AL1" s="58"/>
-      <c r="AM1" s="58"/>
-      <c r="AN1" s="58"/>
-      <c r="AO1" s="58"/>
-      <c r="AP1" s="58"/>
-      <c r="AQ1" s="58"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
+      <c r="L1" s="65"/>
+      <c r="M1" s="65"/>
+      <c r="N1" s="65"/>
+      <c r="O1" s="65"/>
+      <c r="P1" s="65"/>
+      <c r="Q1" s="65"/>
+      <c r="R1" s="65"/>
+      <c r="S1" s="65"/>
+      <c r="T1" s="65"/>
+      <c r="U1" s="65"/>
+      <c r="V1" s="65"/>
+      <c r="W1" s="65"/>
+      <c r="X1" s="65"/>
+      <c r="Y1" s="65"/>
+      <c r="Z1" s="65"/>
+      <c r="AA1" s="65"/>
+      <c r="AB1" s="65"/>
+      <c r="AC1" s="65"/>
+      <c r="AD1" s="65"/>
+      <c r="AE1" s="65"/>
+      <c r="AF1" s="65"/>
+      <c r="AG1" s="65"/>
+      <c r="AH1" s="65"/>
+      <c r="AI1" s="65"/>
+      <c r="AJ1" s="65"/>
+      <c r="AK1" s="65"/>
+      <c r="AL1" s="65"/>
+      <c r="AM1" s="65"/>
+      <c r="AN1" s="65"/>
+      <c r="AO1" s="65"/>
+      <c r="AP1" s="65"/>
+      <c r="AQ1" s="65"/>
       <c r="AR1" s="44"/>
-      <c r="AS1" s="59" t="s">
+      <c r="AS1" s="66" t="s">
         <v>754</v>
       </c>
-      <c r="AT1" s="59"/>
-      <c r="AU1" s="59"/>
-      <c r="AV1" s="59"/>
-      <c r="AW1" s="59"/>
-      <c r="AX1" s="59"/>
-      <c r="AY1" s="59"/>
-      <c r="AZ1" s="59"/>
-      <c r="BA1" s="59"/>
-      <c r="BB1" s="59"/>
-      <c r="BC1" s="59"/>
-      <c r="BD1" s="59"/>
+      <c r="AT1" s="66"/>
+      <c r="AU1" s="66"/>
+      <c r="AV1" s="66"/>
+      <c r="AW1" s="66"/>
+      <c r="AX1" s="66"/>
+      <c r="AY1" s="66"/>
+      <c r="AZ1" s="66"/>
+      <c r="BA1" s="66"/>
+      <c r="BB1" s="66"/>
+      <c r="BC1" s="66"/>
+      <c r="BD1" s="66"/>
     </row>
     <row r="2" spans="1:56" s="25" customFormat="1" ht="97.2" x14ac:dyDescent="0.3">
       <c r="A2" s="25" t="s">
